--- a/T41_V012_Files/T41_V012_Assembled_PCBs_V12.8/Files/T41-Single-PE4312-Attenuator-daughterboard_031426/T41-Single-PE4312-Attenuator-daughterboard-Assy_BOM.xlsx
+++ b/T41_V012_Files/T41_V012_Assembled_PCBs_V12.8/Files/T41-Single-PE4312-Attenuator-daughterboard_031426/T41-Single-PE4312-Attenuator-daughterboard-Assy_BOM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dad\Documents\GitHub\T41\T41_V012_Files\T41_V012_Assembled_PCBs\T41_RF_Board_AttenuatorDaughterboard_V1_031426\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bill\Documents\GitHub\T41\T41_V012_Files\T41_V012_Assembled_PCBs_V12.8\Files\T41-Single-PE4312-Attenuator-daughterboard_031426\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{326C4651-42B7-4815-86B4-EFB6373F6491}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EC2FDD2-DCD6-484B-A78C-1721CF776A42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{E6C0461D-248E-4A4E-92B0-0B75F2E9898F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{E6C0461D-248E-4A4E-92B0-0B75F2E9898F}"/>
   </bookViews>
   <sheets>
     <sheet name="T41-RF-board-AttenuatorDaughter" sheetId="1" r:id="rId1"/>
@@ -52,21 +52,12 @@
     <t>C696359</t>
   </si>
   <si>
-    <t>Ferrite bead 600 mOhm 1A 0603 SMD</t>
-  </si>
-  <si>
     <t>L1</t>
   </si>
   <si>
-    <t>10K Ohm 1/8W 1%</t>
-  </si>
-  <si>
     <t>R1, R2</t>
   </si>
   <si>
-    <t>C161803</t>
-  </si>
-  <si>
     <t>PE4312C-Z Attenuator 20 Lead 4x4 QFN</t>
   </si>
   <si>
@@ -85,7 +76,16 @@
     <t>0603</t>
   </si>
   <si>
-    <t>C1149515</t>
+    <t>Ferrite bead 600 mOhm 1.3A 0603 SMD</t>
+  </si>
+  <si>
+    <t>C85833</t>
+  </si>
+  <si>
+    <t>10K Ohm 1/8W 0.1%</t>
+  </si>
+  <si>
+    <t>C95204</t>
   </si>
 </sst>
 </file>
@@ -963,15 +963,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{016F837E-E3A0-472F-BD90-F2CC1CD50AAA}">
   <dimension ref="A1:G9"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="44.7265625" customWidth="1"/>
-    <col min="2" max="2" width="15.81640625" customWidth="1"/>
-    <col min="3" max="3" width="30.08984375" style="4" customWidth="1"/>
-    <col min="4" max="4" width="21.81640625" customWidth="1"/>
+    <col min="1" max="1" width="44.77734375" customWidth="1"/>
+    <col min="2" max="2" width="15.77734375" customWidth="1"/>
+    <col min="3" max="3" width="30.109375" style="4" customWidth="1"/>
+    <col min="4" max="4" width="21.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -985,7 +985,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -993,13 +993,13 @@
         <v>5</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1007,66 +1007,66 @@
         <v>8</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" t="s">
         <v>10</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="C5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>12</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B6" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="C6" s="4" t="s">
         <v>14</v>
       </c>
+      <c r="D6" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" t="s">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>19</v>
-      </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F9" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G9" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/T41_V012_Files/T41_V012_Assembled_PCBs_V12.8/Files/T41-Single-PE4312-Attenuator-daughterboard_031426/T41-Single-PE4312-Attenuator-daughterboard-Assy_BOM.xlsx
+++ b/T41_V012_Files/T41_V012_Assembled_PCBs_V12.8/Files/T41-Single-PE4312-Attenuator-daughterboard_031426/T41-Single-PE4312-Attenuator-daughterboard-Assy_BOM.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
